--- a/static/data/exports/Retro_GA_GE_2024.xlsx
+++ b/static/data/exports/Retro_GA_GE_2024.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -11799,7 +11799,7 @@
         </is>
       </c>
       <c r="Q183" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R183" t="n">
         <v>53</v>
@@ -12357,7 +12357,7 @@
         </is>
       </c>
       <c r="Q192" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R192" t="n">
         <v>53</v>
@@ -12915,7 +12915,7 @@
         </is>
       </c>
       <c r="Q201" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R201" t="n">
         <v>53</v>
@@ -13473,7 +13473,7 @@
         </is>
       </c>
       <c r="Q210" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R210" t="n">
         <v>53</v>
@@ -14031,7 +14031,7 @@
         </is>
       </c>
       <c r="Q219" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R219" t="n">
         <v>53</v>
@@ -14589,7 +14589,7 @@
         </is>
       </c>
       <c r="Q228" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R228" t="n">
         <v>53</v>
@@ -15085,7 +15085,7 @@
         </is>
       </c>
       <c r="Q236" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R236" t="n">
         <v>53</v>
@@ -15643,7 +15643,7 @@
         </is>
       </c>
       <c r="Q245" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R245" t="n">
         <v>53</v>
@@ -16201,7 +16201,7 @@
         </is>
       </c>
       <c r="Q254" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R254" t="n">
         <v>53</v>
@@ -16759,7 +16759,7 @@
         </is>
       </c>
       <c r="Q263" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R263" t="n">
         <v>53</v>
@@ -17379,7 +17379,7 @@
         </is>
       </c>
       <c r="Q273" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R273" t="n">
         <v>53</v>
@@ -17875,7 +17875,7 @@
         </is>
       </c>
       <c r="Q281" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R281" t="n">
         <v>53</v>
@@ -18433,7 +18433,7 @@
         </is>
       </c>
       <c r="Q290" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R290" t="n">
         <v>53</v>
@@ -18991,7 +18991,7 @@
         </is>
       </c>
       <c r="Q299" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R299" t="n">
         <v>53</v>
@@ -19549,7 +19549,7 @@
         </is>
       </c>
       <c r="Q308" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R308" t="n">
         <v>53</v>
@@ -20107,7 +20107,7 @@
         </is>
       </c>
       <c r="Q317" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R317" t="n">
         <v>53</v>
@@ -20727,7 +20727,7 @@
         </is>
       </c>
       <c r="Q327" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R327" t="n">
         <v>53</v>
@@ -21285,7 +21285,7 @@
         </is>
       </c>
       <c r="Q336" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R336" t="n">
         <v>53</v>
@@ -21843,7 +21843,7 @@
         </is>
       </c>
       <c r="Q345" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R345" t="n">
         <v>53</v>
@@ -22401,7 +22401,7 @@
         </is>
       </c>
       <c r="Q354" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R354" t="n">
         <v>53</v>
